--- a/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语八年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语八年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D258"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -966,6 +966,16 @@
           <t>in need</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在危难中；需要帮助的；在困难时</t>
@@ -978,6 +988,16 @@
           <t>voluntary work</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 义工；义务工作；志愿工作</t>
@@ -990,6 +1010,16 @@
           <t>ask permission</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1002,6 +1032,16 @@
           <t>suffer from</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 患（某种病），受（某种病痛）折磨; 因…而受罚[苦，损]; 闹; 罹</t>
@@ -1014,6 +1054,16 @@
           <t>raise one's spirits</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1024,6 +1074,16 @@
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>in order to</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1644,6 +1704,16 @@
           <t>body language</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 身势语
@@ -1657,6 +1727,16 @@
           <t>take place</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 发生；举行
@@ -1693,6 +1773,16 @@
           <t>make a good impression on ...</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 留下好印象；留一个好的印象；给……留下好印象</t>
@@ -1703,6 +1793,16 @@
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>remind sb. about sth.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2359,6 +2459,16 @@
           <t>paper cutting</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【艺,文】剪纸(艺术)
@@ -2372,6 +2482,16 @@
           <t>up to</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 干(着)；到；胜任；…的责任
@@ -2431,6 +2551,16 @@
           <t>after dark</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. (美国)《夜晚》杂志
@@ -2444,6 +2574,16 @@
           <t>no more</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (此后)不再；死了；…也不[没有]
@@ -2455,6 +2595,16 @@
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>all the time</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3139,6 +3289,16 @@
           <t>comic strip</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. （常登载于报纸上的）连环漫画
@@ -3152,6 +3312,16 @@
           <t>pop out</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (火,把火)突然灭掉；突然伸出；〔俚语〕(突然)死掉
@@ -3165,6 +3335,16 @@
           <t>decide on</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 决心
@@ -3178,6 +3358,16 @@
           <t>video camera</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 摄像机
@@ -3191,6 +3381,16 @@
           <t>play against</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 对赛；同……比赛；与……比赛</t>
@@ -3203,6 +3403,16 @@
           <t>weather forecast</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 天气预报
@@ -3239,6 +3449,16 @@
           <t>thank goodness</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 谢天谢地；自动向某人致谢
@@ -3250,6 +3470,16 @@
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>make it</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -3800,6 +4030,16 @@
           <t>in the wild</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在野外；在自然环境下；处于野生状态</t>
@@ -3812,6 +4052,16 @@
           <t>at birth</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在出生时；刚出生；生下来时</t>
@@ -3824,6 +4074,16 @@
           <t>on one's own</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 独自地；独立地；凭自己力量；主动地
@@ -3835,6 +4095,16 @@
       <c r="A157" s="2" t="inlineStr">
         <is>
           <t>close to</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -4081,6 +4351,16 @@
       <c r="A168" s="2" t="inlineStr">
         <is>
           <t>according to</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -4375,6 +4655,16 @@
           <t>heart attack</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 心脏病发作
@@ -4411,6 +4701,16 @@
           <t>care for</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 照顾；关心；喜欢
@@ -4424,6 +4724,16 @@
           <t>what's more</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 而且；另外；更重要的是</t>
@@ -4436,6 +4746,16 @@
           <t>have no choice but to do</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 除…外别无他法
@@ -4449,6 +4769,16 @@
           <t>run free</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 自由自在地跑
@@ -4462,6 +4792,16 @@
           <t>lie around</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 无所事事；点缀；四处躺着</t>
@@ -4474,6 +4814,16 @@
           <t>keep sb. from sth.</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 避开；禁止；抑制；隐瞒
@@ -4487,6 +4837,16 @@
           <t>keep sb. from doing sth.</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 避免做；避免做某事；从某事中停下来</t>
@@ -4499,6 +4859,16 @@
           <t>faithful to ...</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 忠于；忠实于；忠心于</t>
@@ -4511,6 +4881,16 @@
           <t>be faithful to ...</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 忠于；对……忠诚；忠诚于</t>
@@ -4523,6 +4903,16 @@
           <t>die of</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 因…而死
@@ -4534,6 +4924,16 @@
       <c r="A193" s="2" t="inlineStr">
         <is>
           <t>keep on</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -5222,6 +5622,16 @@
           <t>keep quiet</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (对某事)保守秘密
@@ -5235,6 +5645,16 @@
           <t>because of</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 因
@@ -5248,6 +5668,16 @@
           <t>in fear</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 害怕地；在恐惧中；惊恐地</t>
@@ -5260,6 +5690,16 @@
           <t>landing site</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 着陆点；着陆场
@@ -5273,6 +5713,16 @@
           <t>as soon as possible</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 尽快
@@ -5286,6 +5736,16 @@
           <t>agree with</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 适合；赞同；与…一致
@@ -5297,6 +5757,16 @@
       <c r="A228" s="2" t="inlineStr">
         <is>
           <t>disagree with</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -5846,6 +6316,16 @@
           <t>in the present</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -5858,6 +6338,16 @@
           <t>at the front</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在前面；在前线；在前部</t>
@@ -5870,6 +6360,16 @@
           <t>on the Internet</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在互联网上；在网上；论因特网</t>
@@ -5882,6 +6382,16 @@
           <t>in the shape of</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 以…的形状；呈…的形状；以…的形式；作为…
@@ -5895,6 +6405,16 @@
           <t>mix ... with ...</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 混合
@@ -5908,6 +6428,16 @@
           <t>prepare for</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 准备；为…作准备；为…做准备</t>
@@ -5918,6 +6448,16 @@
       <c r="A258" s="2" t="inlineStr">
         <is>
           <t>in a second</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
